--- a/output/Data and Chart Outputs/poland_gazsystem_points_daily.xlsx
+++ b/output/Data and Chart Outputs/poland_gazsystem_points_daily.xlsx
@@ -155,6 +155,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Poland gas entry points (Gaz-System) (to Sep/26)</a:t>
             </a:r>
           </a:p>
@@ -919,7 +920,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-05 00:35 UTC; 2102 days 2021-01-01 to 2026-10-03</t>
+          <t>2026-10-28 00:56 UTC; 2125 days 2021-01-01 to 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -2736,22 +2737,22 @@
         <v>46266</v>
       </c>
       <c r="D70" t="n">
-        <v>3.951682</v>
+        <v>3.939532</v>
       </c>
       <c r="E70" t="n">
-        <v>1.117722</v>
+        <v>1.11774</v>
       </c>
       <c r="F70" t="n">
-        <v>0.247769</v>
+        <v>0.247775</v>
       </c>
       <c r="G70" t="n">
-        <v>0.001169</v>
+        <v>0.001167</v>
       </c>
       <c r="H70" t="n">
-        <v>5.038611</v>
+        <v>5.03863</v>
       </c>
       <c r="I70" t="n">
-        <v>1.740383</v>
+        <v>1.741107</v>
       </c>
     </row>
   </sheetData>
@@ -2766,7 +2767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P2103"/>
+  <dimension ref="A1:P2126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -99184,10 +99185,10 @@
         <v>46266</v>
       </c>
       <c r="D2071" t="n">
-        <v>149.634</v>
+        <v>149.636</v>
       </c>
       <c r="E2071" t="n">
-        <v>41.463</v>
+        <v>41.462</v>
       </c>
       <c r="F2071" t="n">
         <v>0</v>
@@ -99202,7 +99203,7 @@
         <v>248.154</v>
       </c>
       <c r="J2071" t="n">
-        <v>58.291</v>
+        <v>58.301</v>
       </c>
       <c r="K2071" t="n">
         <v>0</v>
@@ -99228,7 +99229,7 @@
         <v>46267</v>
       </c>
       <c r="D2072" t="n">
-        <v>143.071</v>
+        <v>143.08</v>
       </c>
       <c r="E2072" t="n">
         <v>41.456</v>
@@ -99240,13 +99241,13 @@
         <v>0</v>
       </c>
       <c r="H2072" t="n">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
       <c r="I2072" t="n">
         <v>250.963</v>
       </c>
       <c r="J2072" t="n">
-        <v>57.142</v>
+        <v>57.152</v>
       </c>
       <c r="K2072" t="n">
         <v>9.968999999999999</v>
@@ -99272,7 +99273,7 @@
         <v>46268</v>
       </c>
       <c r="D2073" t="n">
-        <v>143.07</v>
+        <v>143.041</v>
       </c>
       <c r="E2073" t="n">
         <v>41.904</v>
@@ -99290,13 +99291,13 @@
         <v>248.544</v>
       </c>
       <c r="J2073" t="n">
-        <v>58.556</v>
+        <v>58.568</v>
       </c>
       <c r="K2073" t="n">
         <v>0.001</v>
       </c>
       <c r="L2073" t="n">
-        <v>131.641</v>
+        <v>131.642</v>
       </c>
       <c r="M2073" t="n">
         <v>143.075</v>
@@ -99316,10 +99317,10 @@
         <v>46269</v>
       </c>
       <c r="D2074" t="n">
-        <v>143.051</v>
+        <v>143.056</v>
       </c>
       <c r="E2074" t="n">
-        <v>40.59</v>
+        <v>40.591</v>
       </c>
       <c r="F2074" t="n">
         <v>0</v>
@@ -99334,16 +99335,16 @@
         <v>242.85</v>
       </c>
       <c r="J2074" t="n">
-        <v>59.113</v>
+        <v>59.127</v>
       </c>
       <c r="K2074" t="n">
         <v>0</v>
       </c>
       <c r="L2074" t="n">
-        <v>175.171</v>
+        <v>175.173</v>
       </c>
       <c r="M2074" t="n">
-        <v>143.144</v>
+        <v>143.143</v>
       </c>
       <c r="N2074" t="n">
         <v>0</v>
@@ -99360,7 +99361,7 @@
         <v>46270</v>
       </c>
       <c r="D2075" t="n">
-        <v>143.129</v>
+        <v>143.128</v>
       </c>
       <c r="E2075" t="n">
         <v>39.404</v>
@@ -99378,7 +99379,7 @@
         <v>234.516</v>
       </c>
       <c r="J2075" t="n">
-        <v>59.737</v>
+        <v>59.749</v>
       </c>
       <c r="K2075" t="n">
         <v>0</v>
@@ -99404,10 +99405,10 @@
         <v>46271</v>
       </c>
       <c r="D2076" t="n">
-        <v>143.229</v>
+        <v>143.217</v>
       </c>
       <c r="E2076" t="n">
-        <v>38.117</v>
+        <v>38.118</v>
       </c>
       <c r="F2076" t="n">
         <v>0</v>
@@ -99422,7 +99423,7 @@
         <v>245.297</v>
       </c>
       <c r="J2076" t="n">
-        <v>60.008</v>
+        <v>60.019</v>
       </c>
       <c r="K2076" t="n">
         <v>0.323</v>
@@ -99448,7 +99449,7 @@
         <v>46272</v>
       </c>
       <c r="D2077" t="n">
-        <v>143.019</v>
+        <v>143.017</v>
       </c>
       <c r="E2077" t="n">
         <v>14.255</v>
@@ -99466,13 +99467,13 @@
         <v>253.791</v>
       </c>
       <c r="J2077" t="n">
-        <v>58.46</v>
+        <v>58.472</v>
       </c>
       <c r="K2077" t="n">
-        <v>0.304</v>
+        <v>0</v>
       </c>
       <c r="L2077" t="n">
-        <v>135.61</v>
+        <v>135.517</v>
       </c>
       <c r="M2077" t="n">
         <v>142.944</v>
@@ -99510,13 +99511,13 @@
         <v>240.487</v>
       </c>
       <c r="J2078" t="n">
-        <v>58.237</v>
+        <v>58.246</v>
       </c>
       <c r="K2078" t="n">
-        <v>0.031</v>
+        <v>0</v>
       </c>
       <c r="L2078" t="n">
-        <v>130.406</v>
+        <v>130.416</v>
       </c>
       <c r="M2078" t="n">
         <v>143.25</v>
@@ -99536,7 +99537,7 @@
         <v>46274</v>
       </c>
       <c r="D2079" t="n">
-        <v>143.518</v>
+        <v>143.522</v>
       </c>
       <c r="E2079" t="n">
         <v>13.936</v>
@@ -99554,13 +99555,13 @@
         <v>235.814</v>
       </c>
       <c r="J2079" t="n">
-        <v>56.929</v>
+        <v>56.94</v>
       </c>
       <c r="K2079" t="n">
-        <v>0.8070000000000001</v>
+        <v>0</v>
       </c>
       <c r="L2079" t="n">
-        <v>130.001</v>
+        <v>130.002</v>
       </c>
       <c r="M2079" t="n">
         <v>143.272</v>
@@ -99580,7 +99581,7 @@
         <v>46275</v>
       </c>
       <c r="D2080" t="n">
-        <v>140.379</v>
+        <v>140.413</v>
       </c>
       <c r="E2080" t="n">
         <v>17.998</v>
@@ -99598,13 +99599,13 @@
         <v>240.171</v>
       </c>
       <c r="J2080" t="n">
-        <v>57.248</v>
+        <v>57.259</v>
       </c>
       <c r="K2080" t="n">
         <v>0</v>
       </c>
       <c r="L2080" t="n">
-        <v>114.92</v>
+        <v>114.902</v>
       </c>
       <c r="M2080" t="n">
         <v>125.959</v>
@@ -99624,10 +99625,10 @@
         <v>46276</v>
       </c>
       <c r="D2081" t="n">
-        <v>144.522</v>
+        <v>144.528</v>
       </c>
       <c r="E2081" t="n">
-        <v>39</v>
+        <v>39.004</v>
       </c>
       <c r="F2081" t="n">
         <v>0</v>
@@ -99642,16 +99643,16 @@
         <v>179.614</v>
       </c>
       <c r="J2081" t="n">
-        <v>56.581</v>
+        <v>56.616</v>
       </c>
       <c r="K2081" t="n">
         <v>0.014</v>
       </c>
       <c r="L2081" t="n">
-        <v>59.236</v>
+        <v>57.122</v>
       </c>
       <c r="M2081" t="n">
-        <v>149.196</v>
+        <v>148.941</v>
       </c>
       <c r="N2081" t="n">
         <v>0</v>
@@ -99668,10 +99669,10 @@
         <v>46277</v>
       </c>
       <c r="D2082" t="n">
-        <v>122.883</v>
+        <v>121.764</v>
       </c>
       <c r="E2082" t="n">
-        <v>39.014</v>
+        <v>39.015</v>
       </c>
       <c r="F2082" t="n">
         <v>0</v>
@@ -99686,7 +99687,7 @@
         <v>159.236</v>
       </c>
       <c r="J2082" t="n">
-        <v>57.192</v>
+        <v>57.23</v>
       </c>
       <c r="K2082" t="n">
         <v>0.007</v>
@@ -99712,7 +99713,7 @@
         <v>46278</v>
       </c>
       <c r="D2083" t="n">
-        <v>129.073</v>
+        <v>121.81</v>
       </c>
       <c r="E2083" t="n">
         <v>38.986</v>
@@ -99730,7 +99731,7 @@
         <v>157.375</v>
       </c>
       <c r="J2083" t="n">
-        <v>59.349</v>
+        <v>59.364</v>
       </c>
       <c r="K2083" t="n">
         <v>0.007</v>
@@ -99756,7 +99757,7 @@
         <v>46279</v>
       </c>
       <c r="D2084" t="n">
-        <v>132.674</v>
+        <v>129.921</v>
       </c>
       <c r="E2084" t="n">
         <v>41.368</v>
@@ -99774,13 +99775,13 @@
         <v>169.346</v>
       </c>
       <c r="J2084" t="n">
-        <v>57.561</v>
+        <v>57.568</v>
       </c>
       <c r="K2084" t="n">
         <v>0.117</v>
       </c>
       <c r="L2084" t="n">
-        <v>62.169</v>
+        <v>62.171</v>
       </c>
       <c r="M2084" t="n">
         <v>128.951</v>
@@ -99800,7 +99801,7 @@
         <v>46280</v>
       </c>
       <c r="D2085" t="n">
-        <v>135.291</v>
+        <v>135.163</v>
       </c>
       <c r="E2085" t="n">
         <v>41.405</v>
@@ -99818,13 +99819,13 @@
         <v>154.315</v>
       </c>
       <c r="J2085" t="n">
-        <v>56.815</v>
+        <v>56.829</v>
       </c>
       <c r="K2085" t="n">
         <v>0.007</v>
       </c>
       <c r="L2085" t="n">
-        <v>46.503</v>
+        <v>46.915</v>
       </c>
       <c r="M2085" t="n">
         <v>129.324</v>
@@ -99844,7 +99845,7 @@
         <v>46281</v>
       </c>
       <c r="D2086" t="n">
-        <v>128.187</v>
+        <v>128.295</v>
       </c>
       <c r="E2086" t="n">
         <v>41.445</v>
@@ -99859,10 +99860,10 @@
         <v>0.003</v>
       </c>
       <c r="I2086" t="n">
-        <v>103.915</v>
+        <v>103.924</v>
       </c>
       <c r="J2086" t="n">
-        <v>56.103</v>
+        <v>56.116</v>
       </c>
       <c r="K2086" t="n">
         <v>27.992</v>
@@ -99888,7 +99889,7 @@
         <v>46282</v>
       </c>
       <c r="D2087" t="n">
-        <v>130.196</v>
+        <v>130.243</v>
       </c>
       <c r="E2087" t="n">
         <v>41.49</v>
@@ -99906,7 +99907,7 @@
         <v>105.182</v>
       </c>
       <c r="J2087" t="n">
-        <v>56.449</v>
+        <v>56.454</v>
       </c>
       <c r="K2087" t="n">
         <v>14.715</v>
@@ -99932,10 +99933,10 @@
         <v>46283</v>
       </c>
       <c r="D2088" t="n">
-        <v>127.66</v>
+        <v>127.567</v>
       </c>
       <c r="E2088" t="n">
-        <v>40.349</v>
+        <v>40.351</v>
       </c>
       <c r="F2088" t="n">
         <v>0</v>
@@ -99950,7 +99951,7 @@
         <v>119.302</v>
       </c>
       <c r="J2088" t="n">
-        <v>56.016</v>
+        <v>56.024</v>
       </c>
       <c r="K2088" t="n">
         <v>3.332</v>
@@ -99976,7 +99977,7 @@
         <v>46284</v>
       </c>
       <c r="D2089" t="n">
-        <v>127.715</v>
+        <v>127.585</v>
       </c>
       <c r="E2089" t="n">
         <v>39.005</v>
@@ -99994,7 +99995,7 @@
         <v>98.797</v>
       </c>
       <c r="J2089" t="n">
-        <v>57.199</v>
+        <v>57.213</v>
       </c>
       <c r="K2089" t="n">
         <v>0.008</v>
@@ -100020,7 +100021,7 @@
         <v>46285</v>
       </c>
       <c r="D2090" t="n">
-        <v>119.476</v>
+        <v>119.327</v>
       </c>
       <c r="E2090" t="n">
         <v>39.017</v>
@@ -100038,7 +100039,7 @@
         <v>91.681</v>
       </c>
       <c r="J2090" t="n">
-        <v>57.791</v>
+        <v>57.807</v>
       </c>
       <c r="K2090" t="n">
         <v>0</v>
@@ -100064,7 +100065,7 @@
         <v>46286</v>
       </c>
       <c r="D2091" t="n">
-        <v>114.873</v>
+        <v>114.651</v>
       </c>
       <c r="E2091" t="n">
         <v>41.571</v>
@@ -100079,10 +100080,10 @@
         <v>0.004</v>
       </c>
       <c r="I2091" t="n">
-        <v>148.964</v>
+        <v>148.974</v>
       </c>
       <c r="J2091" t="n">
-        <v>57.687</v>
+        <v>57.696</v>
       </c>
       <c r="K2091" t="n">
         <v>0.016</v>
@@ -100108,10 +100109,10 @@
         <v>46287</v>
       </c>
       <c r="D2092" t="n">
-        <v>126.994</v>
+        <v>127.017</v>
       </c>
       <c r="E2092" t="n">
-        <v>43.237</v>
+        <v>43.238</v>
       </c>
       <c r="F2092" t="n">
         <v>0</v>
@@ -100126,19 +100127,19 @@
         <v>200.688</v>
       </c>
       <c r="J2092" t="n">
-        <v>57.612</v>
+        <v>57.619</v>
       </c>
       <c r="K2092" t="n">
         <v>4.631</v>
       </c>
       <c r="L2092" t="n">
-        <v>44.578</v>
+        <v>44.574</v>
       </c>
       <c r="M2092" t="n">
         <v>116.043</v>
       </c>
       <c r="N2092" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="O2092" t="n">
         <v>8.134</v>
@@ -100152,7 +100153,7 @@
         <v>46288</v>
       </c>
       <c r="D2093" t="n">
-        <v>128.645</v>
+        <v>128.7</v>
       </c>
       <c r="E2093" t="n">
         <v>43.332</v>
@@ -100170,7 +100171,7 @@
         <v>248.77</v>
       </c>
       <c r="J2093" t="n">
-        <v>57.004</v>
+        <v>57.011</v>
       </c>
       <c r="K2093" t="n">
         <v>54.382</v>
@@ -100182,7 +100183,7 @@
         <v>118.675</v>
       </c>
       <c r="N2093" t="n">
-        <v>0</v>
+        <v>0.014</v>
       </c>
       <c r="O2093" t="n">
         <v>4.344</v>
@@ -100196,13 +100197,13 @@
         <v>46289</v>
       </c>
       <c r="D2094" t="n">
-        <v>134.865</v>
+        <v>134.934</v>
       </c>
       <c r="E2094" t="n">
         <v>41.408</v>
       </c>
       <c r="F2094" t="n">
-        <v>26.744</v>
+        <v>26.785</v>
       </c>
       <c r="G2094" t="n">
         <v>0</v>
@@ -100214,7 +100215,7 @@
         <v>164.365</v>
       </c>
       <c r="J2094" t="n">
-        <v>57.528</v>
+        <v>57.54</v>
       </c>
       <c r="K2094" t="n">
         <v>8.945</v>
@@ -100240,13 +100241,13 @@
         <v>46290</v>
       </c>
       <c r="D2095" t="n">
-        <v>136.855</v>
+        <v>136.395</v>
       </c>
       <c r="E2095" t="n">
-        <v>41.404</v>
+        <v>41.405</v>
       </c>
       <c r="F2095" t="n">
-        <v>61.781</v>
+        <v>61.71</v>
       </c>
       <c r="G2095" t="n">
         <v>0</v>
@@ -100258,7 +100259,7 @@
         <v>106.559</v>
       </c>
       <c r="J2095" t="n">
-        <v>58.59</v>
+        <v>58.605</v>
       </c>
       <c r="K2095" t="n">
         <v>0</v>
@@ -100284,13 +100285,13 @@
         <v>46291</v>
       </c>
       <c r="D2096" t="n">
-        <v>108.508</v>
+        <v>108.541</v>
       </c>
       <c r="E2096" t="n">
-        <v>41.407</v>
+        <v>41.408</v>
       </c>
       <c r="F2096" t="n">
-        <v>42.883</v>
+        <v>42.919</v>
       </c>
       <c r="G2096" t="n">
         <v>0</v>
@@ -100302,7 +100303,7 @@
         <v>56.387</v>
       </c>
       <c r="J2096" t="n">
-        <v>59.398</v>
+        <v>59.414</v>
       </c>
       <c r="K2096" t="n">
         <v>0</v>
@@ -100328,13 +100329,13 @@
         <v>46292</v>
       </c>
       <c r="D2097" t="n">
-        <v>108.48</v>
+        <v>108.494</v>
       </c>
       <c r="E2097" t="n">
-        <v>41.401</v>
+        <v>41.4</v>
       </c>
       <c r="F2097" t="n">
-        <v>18.907</v>
+        <v>18.897</v>
       </c>
       <c r="G2097" t="n">
         <v>0</v>
@@ -100346,7 +100347,7 @@
         <v>59.196</v>
       </c>
       <c r="J2097" t="n">
-        <v>59.052</v>
+        <v>59.065</v>
       </c>
       <c r="K2097" t="n">
         <v>0</v>
@@ -100372,13 +100373,13 @@
         <v>46293</v>
       </c>
       <c r="D2098" t="n">
-        <v>114.921</v>
+        <v>112.068</v>
       </c>
       <c r="E2098" t="n">
         <v>41.399</v>
       </c>
       <c r="F2098" t="n">
-        <v>1.901</v>
+        <v>1.899</v>
       </c>
       <c r="G2098" t="n">
         <v>0</v>
@@ -100390,7 +100391,7 @@
         <v>80.69</v>
       </c>
       <c r="J2098" t="n">
-        <v>59.323</v>
+        <v>59.34</v>
       </c>
       <c r="K2098" t="n">
         <v>10.699</v>
@@ -100416,16 +100417,16 @@
         <v>46294</v>
       </c>
       <c r="D2099" t="n">
-        <v>121.505</v>
+        <v>122.77</v>
       </c>
       <c r="E2099" t="n">
-        <v>41.393</v>
+        <v>41.405</v>
       </c>
       <c r="F2099" t="n">
-        <v>48.391</v>
+        <v>48.389</v>
       </c>
       <c r="G2099" t="n">
-        <v>0</v>
+        <v>0.046</v>
       </c>
       <c r="H2099" t="n">
         <v>0.005</v>
@@ -100434,7 +100435,7 @@
         <v>86.27500000000001</v>
       </c>
       <c r="J2099" t="n">
-        <v>59.347</v>
+        <v>59.442</v>
       </c>
       <c r="K2099" t="n">
         <v>0</v>
@@ -100460,16 +100461,16 @@
         <v>46295</v>
       </c>
       <c r="D2100" t="n">
-        <v>122.719</v>
+        <v>124.109</v>
       </c>
       <c r="E2100" t="n">
-        <v>36.989</v>
+        <v>36.985</v>
       </c>
       <c r="F2100" t="n">
-        <v>47.162</v>
+        <v>47.176</v>
       </c>
       <c r="G2100" t="n">
-        <v>1.169</v>
+        <v>1.121</v>
       </c>
       <c r="H2100" t="n">
         <v>0.005</v>
@@ -100478,7 +100479,7 @@
         <v>107.367</v>
       </c>
       <c r="J2100" t="n">
-        <v>60.065</v>
+        <v>60.321</v>
       </c>
       <c r="K2100" t="n">
         <v>0</v>
@@ -100493,7 +100494,7 @@
         <v>0</v>
       </c>
       <c r="O2100" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="P2100" t="n">
         <v>0</v>
@@ -100522,7 +100523,7 @@
         <v>114.507</v>
       </c>
       <c r="J2101" t="n">
-        <v>59.777</v>
+        <v>60.049</v>
       </c>
       <c r="K2101" t="n">
         <v>10.35</v>
@@ -100566,7 +100567,7 @@
         <v>91.8</v>
       </c>
       <c r="J2102" t="n">
-        <v>59.238</v>
+        <v>59.553</v>
       </c>
       <c r="K2102" t="n">
         <v>30.307</v>
@@ -100610,7 +100611,7 @@
         <v>62.266</v>
       </c>
       <c r="J2103" t="n">
-        <v>59.395</v>
+        <v>59.715</v>
       </c>
       <c r="K2103" t="n">
         <v>77.18000000000001</v>
@@ -100628,6 +100629,1018 @@
         <v>0</v>
       </c>
       <c r="P2103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2104">
+      <c r="A2104" s="4" t="n">
+        <v>46299</v>
+      </c>
+      <c r="D2104" t="n">
+        <v>122.836</v>
+      </c>
+      <c r="E2104" t="n">
+        <v>19.345</v>
+      </c>
+      <c r="F2104" t="n">
+        <v>16.679</v>
+      </c>
+      <c r="G2104" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2104" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="I2104" t="n">
+        <v>53.01</v>
+      </c>
+      <c r="J2104" t="n">
+        <v>60.426</v>
+      </c>
+      <c r="K2104" t="n">
+        <v>83.798</v>
+      </c>
+      <c r="L2104" t="n">
+        <v>81.82599999999999</v>
+      </c>
+      <c r="M2104" t="n">
+        <v>122.321</v>
+      </c>
+      <c r="N2104" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2104" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2105">
+      <c r="A2105" s="4" t="n">
+        <v>46300</v>
+      </c>
+      <c r="D2105" t="n">
+        <v>123.098</v>
+      </c>
+      <c r="E2105" t="n">
+        <v>20.955</v>
+      </c>
+      <c r="F2105" t="n">
+        <v>17.657</v>
+      </c>
+      <c r="G2105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2105" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="I2105" t="n">
+        <v>51.181</v>
+      </c>
+      <c r="J2105" t="n">
+        <v>58.031</v>
+      </c>
+      <c r="K2105" t="n">
+        <v>84.625</v>
+      </c>
+      <c r="L2105" t="n">
+        <v>54.237</v>
+      </c>
+      <c r="M2105" t="n">
+        <v>122.777</v>
+      </c>
+      <c r="N2105" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2105" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2106">
+      <c r="A2106" s="4" t="n">
+        <v>46301</v>
+      </c>
+      <c r="D2106" t="n">
+        <v>123.007</v>
+      </c>
+      <c r="E2106" t="n">
+        <v>25.954</v>
+      </c>
+      <c r="F2106" t="n">
+        <v>16.299</v>
+      </c>
+      <c r="G2106" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2106" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="I2106" t="n">
+        <v>101.954</v>
+      </c>
+      <c r="J2106" t="n">
+        <v>57.733</v>
+      </c>
+      <c r="K2106" t="n">
+        <v>71.08199999999999</v>
+      </c>
+      <c r="L2106" t="n">
+        <v>55.96</v>
+      </c>
+      <c r="M2106" t="n">
+        <v>124.447</v>
+      </c>
+      <c r="N2106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2106" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2107">
+      <c r="A2107" s="4" t="n">
+        <v>46302</v>
+      </c>
+      <c r="D2107" t="n">
+        <v>122.008</v>
+      </c>
+      <c r="E2107" t="n">
+        <v>25.99</v>
+      </c>
+      <c r="F2107" t="n">
+        <v>15.83</v>
+      </c>
+      <c r="G2107" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2107" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="I2107" t="n">
+        <v>102.315</v>
+      </c>
+      <c r="J2107" t="n">
+        <v>56.088</v>
+      </c>
+      <c r="K2107" t="n">
+        <v>54.22</v>
+      </c>
+      <c r="L2107" t="n">
+        <v>55.81</v>
+      </c>
+      <c r="M2107" t="n">
+        <v>127.024</v>
+      </c>
+      <c r="N2107" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2107" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2108">
+      <c r="A2108" s="4" t="n">
+        <v>46303</v>
+      </c>
+      <c r="D2108" t="n">
+        <v>123.769</v>
+      </c>
+      <c r="E2108" t="n">
+        <v>25.977</v>
+      </c>
+      <c r="F2108" t="n">
+        <v>16.31</v>
+      </c>
+      <c r="G2108" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2108" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="I2108" t="n">
+        <v>96.95999999999999</v>
+      </c>
+      <c r="J2108" t="n">
+        <v>54.343</v>
+      </c>
+      <c r="K2108" t="n">
+        <v>44.712</v>
+      </c>
+      <c r="L2108" t="n">
+        <v>60.013</v>
+      </c>
+      <c r="M2108" t="n">
+        <v>123.899</v>
+      </c>
+      <c r="N2108" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2108" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2109">
+      <c r="A2109" s="4" t="n">
+        <v>46304</v>
+      </c>
+      <c r="D2109" t="n">
+        <v>120.928</v>
+      </c>
+      <c r="E2109" t="n">
+        <v>24.106</v>
+      </c>
+      <c r="F2109" t="n">
+        <v>24.717</v>
+      </c>
+      <c r="G2109" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2109" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="I2109" t="n">
+        <v>116.197</v>
+      </c>
+      <c r="J2109" t="n">
+        <v>54.773</v>
+      </c>
+      <c r="K2109" t="n">
+        <v>50.81</v>
+      </c>
+      <c r="L2109" t="n">
+        <v>64.02500000000001</v>
+      </c>
+      <c r="M2109" t="n">
+        <v>124.935</v>
+      </c>
+      <c r="N2109" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2109" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2110">
+      <c r="A2110" s="4" t="n">
+        <v>46305</v>
+      </c>
+      <c r="D2110" t="n">
+        <v>119.618</v>
+      </c>
+      <c r="E2110" t="n">
+        <v>22.252</v>
+      </c>
+      <c r="F2110" t="n">
+        <v>35.767</v>
+      </c>
+      <c r="G2110" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2110" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="I2110" t="n">
+        <v>118.845</v>
+      </c>
+      <c r="J2110" t="n">
+        <v>56.343</v>
+      </c>
+      <c r="K2110" t="n">
+        <v>55.201</v>
+      </c>
+      <c r="L2110" t="n">
+        <v>66.205</v>
+      </c>
+      <c r="M2110" t="n">
+        <v>123.473</v>
+      </c>
+      <c r="N2110" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2110" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2111">
+      <c r="A2111" s="4" t="n">
+        <v>46306</v>
+      </c>
+      <c r="D2111" t="n">
+        <v>123.017</v>
+      </c>
+      <c r="E2111" t="n">
+        <v>20.656</v>
+      </c>
+      <c r="F2111" t="n">
+        <v>36.633</v>
+      </c>
+      <c r="G2111" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2111" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="I2111" t="n">
+        <v>120.107</v>
+      </c>
+      <c r="J2111" t="n">
+        <v>56.383</v>
+      </c>
+      <c r="K2111" t="n">
+        <v>42.344</v>
+      </c>
+      <c r="L2111" t="n">
+        <v>39.974</v>
+      </c>
+      <c r="M2111" t="n">
+        <v>128.39</v>
+      </c>
+      <c r="N2111" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2111" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2112">
+      <c r="A2112" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="D2112" t="n">
+        <v>127.438</v>
+      </c>
+      <c r="E2112" t="n">
+        <v>26.069</v>
+      </c>
+      <c r="F2112" t="n">
+        <v>36.123</v>
+      </c>
+      <c r="G2112" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2112" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="I2112" t="n">
+        <v>135.071</v>
+      </c>
+      <c r="J2112" t="n">
+        <v>55.033</v>
+      </c>
+      <c r="K2112" t="n">
+        <v>36.434</v>
+      </c>
+      <c r="L2112" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2112" t="n">
+        <v>125.539</v>
+      </c>
+      <c r="N2112" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2112" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2113">
+      <c r="A2113" s="4" t="n">
+        <v>46308</v>
+      </c>
+      <c r="D2113" t="n">
+        <v>126.053</v>
+      </c>
+      <c r="E2113" t="n">
+        <v>38.311</v>
+      </c>
+      <c r="F2113" t="n">
+        <v>34.745</v>
+      </c>
+      <c r="G2113" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2113" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="I2113" t="n">
+        <v>223.373</v>
+      </c>
+      <c r="J2113" t="n">
+        <v>51.996</v>
+      </c>
+      <c r="K2113" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="L2113" t="n">
+        <v>8.461</v>
+      </c>
+      <c r="M2113" t="n">
+        <v>130.804</v>
+      </c>
+      <c r="N2113" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2114">
+      <c r="A2114" s="4" t="n">
+        <v>46309</v>
+      </c>
+      <c r="D2114" t="n">
+        <v>122.279</v>
+      </c>
+      <c r="E2114" t="n">
+        <v>39.26</v>
+      </c>
+      <c r="F2114" t="n">
+        <v>34.834</v>
+      </c>
+      <c r="G2114" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2114" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="I2114" t="n">
+        <v>170.68</v>
+      </c>
+      <c r="J2114" t="n">
+        <v>51.916</v>
+      </c>
+      <c r="K2114" t="n">
+        <v>27.663</v>
+      </c>
+      <c r="L2114" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2114" t="n">
+        <v>134.733</v>
+      </c>
+      <c r="N2114" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2114" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2115">
+      <c r="A2115" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="D2115" t="n">
+        <v>123.955</v>
+      </c>
+      <c r="E2115" t="n">
+        <v>39.016</v>
+      </c>
+      <c r="F2115" t="n">
+        <v>37.627</v>
+      </c>
+      <c r="G2115" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2115" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="I2115" t="n">
+        <v>170.77</v>
+      </c>
+      <c r="J2115" t="n">
+        <v>52.932</v>
+      </c>
+      <c r="K2115" t="n">
+        <v>48.142</v>
+      </c>
+      <c r="L2115" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="M2115" t="n">
+        <v>135.057</v>
+      </c>
+      <c r="N2115" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2115" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2116">
+      <c r="A2116" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="D2116" t="n">
+        <v>131.873</v>
+      </c>
+      <c r="E2116" t="n">
+        <v>35.258</v>
+      </c>
+      <c r="F2116" t="n">
+        <v>35.721</v>
+      </c>
+      <c r="G2116" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2116" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="I2116" t="n">
+        <v>183.246</v>
+      </c>
+      <c r="J2116" t="n">
+        <v>55.928</v>
+      </c>
+      <c r="K2116" t="n">
+        <v>12.859</v>
+      </c>
+      <c r="L2116" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="M2116" t="n">
+        <v>134.846</v>
+      </c>
+      <c r="N2116" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2116" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2117">
+      <c r="A2117" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="D2117" t="n">
+        <v>132.573</v>
+      </c>
+      <c r="E2117" t="n">
+        <v>29.418</v>
+      </c>
+      <c r="F2117" t="n">
+        <v>35.768</v>
+      </c>
+      <c r="G2117" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2117" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="I2117" t="n">
+        <v>171.805</v>
+      </c>
+      <c r="J2117" t="n">
+        <v>56.434</v>
+      </c>
+      <c r="K2117" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2117" t="n">
+        <v>14.55</v>
+      </c>
+      <c r="M2117" t="n">
+        <v>134.942</v>
+      </c>
+      <c r="N2117" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2117" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2118">
+      <c r="A2118" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="D2118" t="n">
+        <v>131.995</v>
+      </c>
+      <c r="E2118" t="n">
+        <v>28.128</v>
+      </c>
+      <c r="F2118" t="n">
+        <v>35.955</v>
+      </c>
+      <c r="G2118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2118" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="I2118" t="n">
+        <v>138.41</v>
+      </c>
+      <c r="J2118" t="n">
+        <v>57.103</v>
+      </c>
+      <c r="K2118" t="n">
+        <v>29.723</v>
+      </c>
+      <c r="L2118" t="n">
+        <v>5.836</v>
+      </c>
+      <c r="M2118" t="n">
+        <v>134.69</v>
+      </c>
+      <c r="N2118" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2118" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2119">
+      <c r="A2119" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="D2119" t="n">
+        <v>132.328</v>
+      </c>
+      <c r="E2119" t="n">
+        <v>30.078</v>
+      </c>
+      <c r="F2119" t="n">
+        <v>34.945</v>
+      </c>
+      <c r="G2119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2119" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I2119" t="n">
+        <v>170.926</v>
+      </c>
+      <c r="J2119" t="n">
+        <v>57.042</v>
+      </c>
+      <c r="K2119" t="n">
+        <v>77.307</v>
+      </c>
+      <c r="L2119" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2119" t="n">
+        <v>134.709</v>
+      </c>
+      <c r="N2119" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2119" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2120">
+      <c r="A2120" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="D2120" t="n">
+        <v>132.113</v>
+      </c>
+      <c r="E2120" t="n">
+        <v>17.002</v>
+      </c>
+      <c r="F2120" t="n">
+        <v>34.84</v>
+      </c>
+      <c r="G2120" t="n">
+        <v>1.511</v>
+      </c>
+      <c r="H2120" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="I2120" t="n">
+        <v>264.44</v>
+      </c>
+      <c r="J2120" t="n">
+        <v>55.763</v>
+      </c>
+      <c r="K2120" t="n">
+        <v>2.045</v>
+      </c>
+      <c r="L2120" t="n">
+        <v>25.985</v>
+      </c>
+      <c r="M2120" t="n">
+        <v>131.948</v>
+      </c>
+      <c r="N2120" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2120" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2121">
+      <c r="A2121" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="D2121" t="n">
+        <v>131.284</v>
+      </c>
+      <c r="E2121" t="n">
+        <v>24.953</v>
+      </c>
+      <c r="F2121" t="n">
+        <v>34.434</v>
+      </c>
+      <c r="G2121" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2121" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="I2121" t="n">
+        <v>230.232</v>
+      </c>
+      <c r="J2121" t="n">
+        <v>56.094</v>
+      </c>
+      <c r="K2121" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="L2121" t="n">
+        <v>40.433</v>
+      </c>
+      <c r="M2121" t="n">
+        <v>131.041</v>
+      </c>
+      <c r="N2121" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2121" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2122">
+      <c r="A2122" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="D2122" t="n">
+        <v>131.434</v>
+      </c>
+      <c r="E2122" t="n">
+        <v>26.996</v>
+      </c>
+      <c r="F2122" t="n">
+        <v>34.538</v>
+      </c>
+      <c r="G2122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2122" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="I2122" t="n">
+        <v>237.239</v>
+      </c>
+      <c r="J2122" t="n">
+        <v>56.801</v>
+      </c>
+      <c r="K2122" t="n">
+        <v>5.006</v>
+      </c>
+      <c r="L2122" t="n">
+        <v>45.029</v>
+      </c>
+      <c r="M2122" t="n">
+        <v>130.827</v>
+      </c>
+      <c r="N2122" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2122" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2123">
+      <c r="A2123" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="D2123" t="n">
+        <v>128.505</v>
+      </c>
+      <c r="E2123" t="n">
+        <v>27.834</v>
+      </c>
+      <c r="F2123" t="n">
+        <v>34.124</v>
+      </c>
+      <c r="G2123" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2123" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="I2123" t="n">
+        <v>224.642</v>
+      </c>
+      <c r="J2123" t="n">
+        <v>55.948</v>
+      </c>
+      <c r="K2123" t="n">
+        <v>7.737</v>
+      </c>
+      <c r="L2123" t="n">
+        <v>36.193</v>
+      </c>
+      <c r="M2123" t="n">
+        <v>131.446</v>
+      </c>
+      <c r="N2123" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2123" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2124">
+      <c r="A2124" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="D2124" t="n">
+        <v>134.918</v>
+      </c>
+      <c r="E2124" t="n">
+        <v>27.574</v>
+      </c>
+      <c r="F2124" t="n">
+        <v>36.335</v>
+      </c>
+      <c r="G2124" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2124" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I2124" t="n">
+        <v>190.232</v>
+      </c>
+      <c r="J2124" t="n">
+        <v>60.962</v>
+      </c>
+      <c r="K2124" t="n">
+        <v>5.746</v>
+      </c>
+      <c r="L2124" t="n">
+        <v>37.852</v>
+      </c>
+      <c r="M2124" t="n">
+        <v>136.319</v>
+      </c>
+      <c r="N2124" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2124" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2125">
+      <c r="A2125" s="4" t="n">
+        <v>46320</v>
+      </c>
+      <c r="D2125" t="n">
+        <v>131.479</v>
+      </c>
+      <c r="E2125" t="n">
+        <v>26.496</v>
+      </c>
+      <c r="F2125" t="n">
+        <v>34.973</v>
+      </c>
+      <c r="G2125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2125" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="I2125" t="n">
+        <v>180.398</v>
+      </c>
+      <c r="J2125" t="n">
+        <v>57.318</v>
+      </c>
+      <c r="K2125" t="n">
+        <v>5.469</v>
+      </c>
+      <c r="L2125" t="n">
+        <v>35.178</v>
+      </c>
+      <c r="M2125" t="n">
+        <v>130.262</v>
+      </c>
+      <c r="N2125" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2125" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2126">
+      <c r="A2126" s="4" t="n">
+        <v>46321</v>
+      </c>
+      <c r="D2126" t="n">
+        <v>130.786</v>
+      </c>
+      <c r="E2126" t="n">
+        <v>27.753</v>
+      </c>
+      <c r="F2126" t="n">
+        <v>34.247</v>
+      </c>
+      <c r="G2126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2126" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I2126" t="n">
+        <v>249.936</v>
+      </c>
+      <c r="J2126" t="n">
+        <v>56.179</v>
+      </c>
+      <c r="K2126" t="n">
+        <v>7.138</v>
+      </c>
+      <c r="L2126" t="n">
+        <v>29.902</v>
+      </c>
+      <c r="M2126" t="n">
+        <v>131.789</v>
+      </c>
+      <c r="N2126" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2126" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2126" t="n">
         <v>0</v>
       </c>
     </row>
